--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:15</t>
+    <t xml:space="preserve">2026-09-09 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:10</t>
+    <t xml:space="preserve">2026-09-17 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:06</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:53</t>
+    <t xml:space="preserve">2026-10-05 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -705,7 +705,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>753554.62</v>
+        <v>753554.63</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>629392.62</v>
+        <v>629392.63</v>
       </c>
     </row>
     <row r="8">
@@ -909,7 +909,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>382639.12</v>
+        <v>382639.13</v>
       </c>
     </row>
     <row r="19">
@@ -1436,7 +1436,7 @@
         <v>2021</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>225400.12</v>
+        <v>225400.13</v>
       </c>
     </row>
     <row r="50">
